--- a/assets/address.xlsx
+++ b/assets/address.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="286">
   <si>
     <t>formation</t>
   </si>
@@ -440,12 +440,12 @@
     <t>Office of Commissioner CGST Audit-I Commissionerate</t>
   </si>
   <si>
+    <t>Null</t>
+  </si>
+  <si>
     <t>4th, B Wing, GST Bhavan, 41/A, Sassoon Road, Pune-411001</t>
   </si>
   <si>
-    <t>Nill</t>
-  </si>
-  <si>
     <t>Technical Section-HQ</t>
   </si>
   <si>
@@ -534,9 +534,6 @@
   </si>
   <si>
     <t>F Wing, East Side, 3rd Floor, 41/A, ICE House, GST Bhavan, Sassoon Road, Pune-411001</t>
-  </si>
-  <si>
-    <t>Null</t>
   </si>
   <si>
     <t>Appeals Receipt Section</t>
@@ -3267,8 +3264,8 @@
     <col customWidth="1" min="1" max="1" width="16.86"/>
     <col customWidth="1" min="2" max="2" width="25.29"/>
     <col customWidth="1" min="3" max="3" width="60.57"/>
-    <col customWidth="1" min="4" max="4" width="62.71"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
+    <col customWidth="1" min="4" max="4" width="35.0"/>
+    <col customWidth="1" min="5" max="5" width="44.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -3290,223 +3287,223 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D3" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>169</v>
+      <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>169</v>
+        <v>188</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>169</v>
+        <v>177</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>169</v>
+        <v>189</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>169</v>
+        <v>190</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>169</v>
+        <v>191</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>169</v>
+        <v>192</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>169</v>
+        <v>173</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>169</v>
+        <v>193</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>169</v>
+        <v>194</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3551,27 +3548,27 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -3585,10 +3582,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>12</v>
@@ -3597,15 +3594,15 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -3614,15 +3611,15 @@
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
@@ -3631,15 +3628,15 @@
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
@@ -3648,15 +3645,15 @@
         <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>17</v>
@@ -3665,15 +3662,15 @@
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>18</v>
@@ -3687,10 +3684,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>20</v>
@@ -3704,10 +3701,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -3721,10 +3718,10 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
@@ -3738,10 +3735,10 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>24</v>
@@ -3750,15 +3747,15 @@
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -3767,15 +3764,15 @@
         <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>27</v>
@@ -3784,15 +3781,15 @@
         <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>28</v>
@@ -3801,35 +3798,35 @@
         <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C17" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>8</v>
@@ -3840,13 +3837,13 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>8</v>
@@ -3857,13 +3854,13 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>8</v>
@@ -3874,27 +3871,27 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>31</v>
@@ -3908,1379 +3905,1379 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C28" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C30" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C32" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C36" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C39" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C40" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C41" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C51" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C58" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C61" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C62" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C63" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C64" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C65" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C67" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C68" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C69" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D69" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D71" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D72" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D73" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C74" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D74" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C75" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D75" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E75" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C76" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C77" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C78" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C79" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C80" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C81" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C83" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C84" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C85" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C86" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C87" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C88" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C89" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C90" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C91" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C92" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C93" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D93" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C94" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D94" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C95" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D95" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C96" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C97" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D97" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C98" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D98" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C99" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D99" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C100" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D100" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E100" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C101" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D101" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C102" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D102" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E102" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="C103" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D103" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -5325,27 +5322,27 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -5354,15 +5351,15 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>12</v>
@@ -5371,15 +5368,15 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -5388,15 +5385,15 @@
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
@@ -5405,15 +5402,15 @@
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
@@ -5422,15 +5419,15 @@
         <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>17</v>
@@ -5439,15 +5436,15 @@
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>18</v>
@@ -5456,15 +5453,15 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>20</v>
@@ -5473,15 +5470,15 @@
         <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -5490,15 +5487,15 @@
         <v>8</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
@@ -5507,15 +5504,15 @@
         <v>8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>24</v>
@@ -5524,15 +5521,15 @@
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -5541,15 +5538,15 @@
         <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>27</v>
@@ -5558,15 +5555,15 @@
         <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>28</v>
@@ -5575,15 +5572,15 @@
         <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>29</v>
@@ -5592,83 +5589,83 @@
         <v>8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>31</v>
@@ -5677,24 +5674,24 @@
         <v>8</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -11276,8 +11273,8 @@
     <col customWidth="1" min="1" max="1" width="14.86"/>
     <col customWidth="1" min="2" max="2" width="34.14"/>
     <col customWidth="1" min="3" max="3" width="59.71"/>
-    <col customWidth="1" min="4" max="4" width="88.14"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
+    <col customWidth="1" min="4" max="4" width="22.86"/>
+    <col customWidth="1" min="5" max="5" width="66.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -11307,10 +11304,10 @@
       <c r="C2" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -11324,11 +11321,11 @@
       <c r="C3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -11341,11 +11338,11 @@
       <c r="C4" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -11358,11 +11355,11 @@
       <c r="C5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -11375,10 +11372,10 @@
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -11392,11 +11389,11 @@
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -11409,11 +11406,11 @@
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -11426,10 +11423,10 @@
       <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -11443,11 +11440,11 @@
       <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -11460,11 +11457,11 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -11477,11 +11474,11 @@
       <c r="C12" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -11494,11 +11491,11 @@
       <c r="C13" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -11511,11 +11508,11 @@
       <c r="C14" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -11528,11 +11525,11 @@
       <c r="C15" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -11545,11 +11542,11 @@
       <c r="C16" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -11562,11 +11559,11 @@
       <c r="C17" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -11579,11 +11576,11 @@
       <c r="C18" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -11605,7 +11602,7 @@
     <col customWidth="1" min="1" max="1" width="14.86"/>
     <col customWidth="1" min="2" max="2" width="34.14"/>
     <col customWidth="1" min="3" max="3" width="59.71"/>
-    <col customWidth="1" min="4" max="4" width="65.43"/>
+    <col customWidth="1" min="4" max="4" width="14.0"/>
     <col customWidth="1" min="5" max="5" width="40.14"/>
   </cols>
   <sheetData>
@@ -11636,11 +11633,11 @@
       <c r="C2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -11653,11 +11650,11 @@
       <c r="C3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -11670,11 +11667,11 @@
       <c r="C4" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -11687,11 +11684,11 @@
       <c r="C5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -11704,11 +11701,11 @@
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -11721,11 +11718,11 @@
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -11738,11 +11735,11 @@
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -11755,11 +11752,11 @@
       <c r="C9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -11772,11 +11769,11 @@
       <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -11789,11 +11786,11 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -11806,11 +11803,11 @@
       <c r="C12" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -11823,11 +11820,11 @@
       <c r="C13" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -11840,11 +11837,11 @@
       <c r="C14" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -11857,11 +11854,11 @@
       <c r="C15" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -11874,11 +11871,11 @@
       <c r="C16" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
@@ -11891,11 +11888,11 @@
       <c r="C17" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -11908,11 +11905,11 @@
       <c r="C18" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -11925,11 +11922,11 @@
       <c r="C19" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -11951,7 +11948,7 @@
     <col customWidth="1" min="1" max="1" width="20.14"/>
     <col customWidth="1" min="2" max="2" width="41.29"/>
     <col customWidth="1" min="3" max="3" width="42.43"/>
-    <col customWidth="1" min="4" max="4" width="77.86"/>
+    <col customWidth="1" min="4" max="4" width="15.29"/>
     <col customWidth="1" min="5" max="5" width="55.29"/>
   </cols>
   <sheetData>
@@ -11982,11 +11979,11 @@
       <c r="C2" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -11997,13 +11994,13 @@
         <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -12014,13 +12011,13 @@
         <v>166</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>169</v>
+      <c r="D4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -12031,13 +12028,13 @@
         <v>166</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -12048,13 +12045,13 @@
         <v>166</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>169</v>
+        <v>173</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -12065,13 +12062,13 @@
         <v>166</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>169</v>
+        <v>174</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -12082,13 +12079,13 @@
         <v>166</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -12099,13 +12096,13 @@
         <v>166</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>169</v>
+        <v>176</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -12116,13 +12113,13 @@
         <v>166</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>169</v>
+        <v>177</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -12144,8 +12141,8 @@
     <col customWidth="1" min="1" max="1" width="20.14"/>
     <col customWidth="1" min="2" max="2" width="41.29"/>
     <col customWidth="1" min="3" max="3" width="42.43"/>
-    <col customWidth="1" min="4" max="4" width="79.86"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
+    <col customWidth="1" min="4" max="4" width="11.71"/>
+    <col customWidth="1" min="5" max="5" width="76.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -12170,16 +12167,16 @@
         <v>165</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -12187,16 +12184,16 @@
         <v>165</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="8" t="s">
         <v>169</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -12204,16 +12201,16 @@
         <v>165</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -12221,16 +12218,16 @@
         <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -12238,16 +12235,16 @@
         <v>165</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>169</v>
+        <v>173</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -12255,16 +12252,16 @@
         <v>165</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>169</v>
+        <v>174</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -12272,16 +12269,16 @@
         <v>165</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -12289,16 +12286,16 @@
         <v>165</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>169</v>
+        <v>176</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -12306,16 +12303,16 @@
         <v>165</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>169</v>
+        <v>177</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1"/>
@@ -13350,16 +13347,16 @@
         <v>165</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -13367,16 +13364,16 @@
         <v>165</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -13384,16 +13381,16 @@
         <v>165</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -13401,16 +13398,16 @@
         <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -13418,16 +13415,16 @@
         <v>165</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -13435,16 +13432,16 @@
         <v>165</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -13452,16 +13449,16 @@
         <v>165</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -13469,16 +13466,16 @@
         <v>165</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -13486,16 +13483,16 @@
         <v>165</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/assets/address.xlsx
+++ b/assets/address.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="287">
   <si>
     <t>formation</t>
   </si>
@@ -486,6 +486,9 @@
   </si>
   <si>
     <t>Plot No. R-45 to 50, Additional MIDC, Satara-415004</t>
+  </si>
+  <si>
+    <t>CGST Audit-II Commissionerate Pune</t>
   </si>
   <si>
     <t>Office of Commissioner CGST Audit-II Commissionerate</t>
@@ -959,7 +962,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -979,6 +982,9 @@
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -3287,223 +3293,223 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3548,27 +3554,27 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
@@ -3577,15 +3583,15 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>12</v>
@@ -3594,15 +3600,15 @@
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -3611,15 +3617,15 @@
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
@@ -3628,15 +3634,15 @@
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
@@ -3645,15 +3651,15 @@
         <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>17</v>
@@ -3662,15 +3668,15 @@
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>18</v>
@@ -3679,15 +3685,15 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>20</v>
@@ -3696,15 +3702,15 @@
         <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -3713,15 +3719,15 @@
         <v>8</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
@@ -3730,15 +3736,15 @@
         <v>8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>24</v>
@@ -3747,15 +3753,15 @@
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
@@ -3764,15 +3770,15 @@
         <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>27</v>
@@ -3781,15 +3787,15 @@
         <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>28</v>
@@ -3798,100 +3804,100 @@
         <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>31</v>
@@ -3900,1384 +3906,1384 @@
         <v>8</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>245</v>
+        <v>239</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>247</v>
+        <v>239</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>249</v>
+        <v>239</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>251</v>
+        <v>239</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>253</v>
+        <v>239</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="E75" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D75" s="11" t="s">
         <v>256</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>41</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -5322,376 +5328,376 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D2" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D19" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D23" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -11627,25 +11633,25 @@
       <c r="A2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>135</v>
+      <c r="B2" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>135</v>
+      <c r="B3" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>139</v>
@@ -11654,15 +11660,15 @@
         <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>135</v>
+      <c r="B4" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>141</v>
@@ -11671,15 +11677,15 @@
         <v>137</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>135</v>
+      <c r="B5" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>142</v>
@@ -11688,15 +11694,15 @@
         <v>137</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>135</v>
+      <c r="B6" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
@@ -11705,15 +11711,15 @@
         <v>137</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>135</v>
+      <c r="B7" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
@@ -11722,15 +11728,15 @@
         <v>137</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>135</v>
+      <c r="B8" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>15</v>
@@ -11739,15 +11745,15 @@
         <v>137</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>135</v>
+      <c r="B9" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>16</v>
@@ -11756,15 +11762,15 @@
         <v>137</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>135</v>
+      <c r="B10" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>17</v>
@@ -11773,15 +11779,15 @@
         <v>137</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>135</v>
+      <c r="B11" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>27</v>
@@ -11790,15 +11796,15 @@
         <v>137</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>135</v>
+      <c r="B12" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>143</v>
@@ -11807,69 +11813,69 @@
         <v>137</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>135</v>
+      <c r="B13" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>135</v>
+      <c r="B14" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>135</v>
+      <c r="B15" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>135</v>
+      <c r="B16" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>137</v>
@@ -11882,11 +11888,11 @@
       <c r="A17" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>135</v>
+      <c r="B17" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>137</v>
@@ -11899,11 +11905,11 @@
       <c r="A18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>135</v>
+      <c r="B18" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>137</v>
@@ -11916,11 +11922,11 @@
       <c r="A19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>135</v>
+      <c r="B19" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>137</v>
@@ -11971,155 +11977,155 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -12164,155 +12170,155 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1"/>
@@ -13344,13 +13350,13 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>137</v>
@@ -13361,13 +13367,13 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>137</v>
@@ -13378,13 +13384,13 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>137</v>
@@ -13395,13 +13401,13 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>137</v>
@@ -13412,13 +13418,13 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>137</v>
@@ -13429,13 +13435,13 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>137</v>
@@ -13446,13 +13452,13 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>137</v>
@@ -13463,13 +13469,13 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>137</v>
@@ -13480,13 +13486,13 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>137</v>
